--- a/tests/fixtures/row_formats/row_formats.xlsx
+++ b/tests/fixtures/row_formats/row_formats.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmp2ob04_j6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmp8pn_8tbf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{247F68A9-1DE2-4836-A536-5E970189B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{610F70AC-3DBE-4515-B9B4-5C6982D5FA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="19440" windowHeight="11220" firstSheet="148" activeTab="148" xr2:uid="{8F60F22F-5708-4683-BFCC-95BF9620423D}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="7920" windowHeight="13995" firstSheet="187" activeTab="187" xr2:uid="{4318A891-E76C-4392-8907-219407430D5D}"/>
   </bookViews>
   <sheets>
     <sheet name="noop_bold_false" sheetId="1" r:id="rId1"/>
@@ -162,6 +162,45 @@
     <sheet name="sheet_size" sheetId="147" r:id="rId147"/>
     <sheet name="row_style_rows_all_height" sheetId="148" r:id="rId148"/>
     <sheet name="unmeasured_row_column_mix" sheetId="149" r:id="rId149"/>
+    <sheet name="edge_bottom_thin" sheetId="150" r:id="rId150"/>
+    <sheet name="edge_bottom_medium" sheetId="151" r:id="rId151"/>
+    <sheet name="edge_bottom_thick" sheetId="152" r:id="rId152"/>
+    <sheet name="edge_bottom_double" sheetId="153" r:id="rId153"/>
+    <sheet name="edge_bottom_mediumDashed" sheetId="154" r:id="rId154"/>
+    <sheet name="edge_bottom_mediumDashDot" sheetId="155" r:id="rId155"/>
+    <sheet name="edge_bottom_mediumDashDotDot" sheetId="156" r:id="rId156"/>
+    <sheet name="edge_bottom_slantDashDot" sheetId="157" r:id="rId157"/>
+    <sheet name="edge_bottom_dashed" sheetId="158" r:id="rId158"/>
+    <sheet name="edge_bottom_hair" sheetId="159" r:id="rId159"/>
+    <sheet name="edge_top_double" sheetId="160" r:id="rId160"/>
+    <sheet name="edge_top_medium" sheetId="161" r:id="rId161"/>
+    <sheet name="edge_row1_top_thick" sheetId="162" r:id="rId162"/>
+    <sheet name="edge_row1_top_medium" sheetId="163" r:id="rId163"/>
+    <sheet name="edge_last_row_double" sheetId="164" r:id="rId164"/>
+    <sheet name="edge_left_double" sheetId="165" r:id="rId165"/>
+    <sheet name="edge_inside_medium" sheetId="166" r:id="rId166"/>
+    <sheet name="edge_inside_double" sheetId="167" r:id="rId167"/>
+    <sheet name="edge_double_both" sheetId="168" r:id="rId168"/>
+    <sheet name="edge_medium_top_and_bottom" sheetId="169" r:id="rId169"/>
+    <sheet name="edge_double_big_font" sheetId="170" r:id="rId170"/>
+    <sheet name="edge_double_small_row" sheetId="171" r:id="rId171"/>
+    <sheet name="edge_double_custom_height" sheetId="172" r:id="rId172"/>
+    <sheet name="edge_double_autofit" sheetId="173" r:id="rId173"/>
+    <sheet name="edge_double_cleared" sheetId="174" r:id="rId174"/>
+    <sheet name="edge_row_style_double" sheetId="175" r:id="rId175"/>
+    <sheet name="edge_far_column" sheetId="176" r:id="rId176"/>
+    <sheet name="edge_value_medium" sheetId="177" r:id="rId177"/>
+    <sheet name="edge_column_inside_double" sheetId="178" r:id="rId178"/>
+    <sheet name="edge_column_inside_medium" sheetId="179" r:id="rId179"/>
+    <sheet name="edge_column_double_value" sheetId="180" r:id="rId180"/>
+    <sheet name="edge_sheet_inside_double" sheetId="181" r:id="rId181"/>
+    <sheet name="edge_mix_medium_double" sheetId="182" r:id="rId182"/>
+    <sheet name="edge_mix_double_medium" sheetId="183" r:id="rId183"/>
+    <sheet name="edge_mix_c_medium_first" sheetId="184" r:id="rId184"/>
+    <sheet name="edge_mix_thin_double" sheetId="185" r:id="rId185"/>
+    <sheet name="edge_mix_top_below" sheetId="186" r:id="rId186"/>
+    <sheet name="edge_mix_row_then_cell" sheetId="187" r:id="rId187"/>
+    <sheet name="unmeasured_edge_hidden_row" sheetId="188" r:id="rId188"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -307,7 +346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -428,11 +467,150 @@
         <color indexed="64"/>
       </diagonal>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="mediumDashed">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="mediumDashDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="mediumDashDotDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="slantDashDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -468,6 +646,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,7 +996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59081F8D-0852-43C3-A2CA-789349C59655}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FC1E2D-351A-4C98-BD89-D58423DA6EAD}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -814,7 +1009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCF9865-24F8-4DC4-8AD7-7768486F0E06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753EE042-C0E8-4730-BF49-260FC393CE40}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -827,7 +1022,7 @@
 </file>
 
 <file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BB987B-7067-4BBF-9DD9-1A6CC902290E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAC9B7F-328B-4CCA-8715-84FC944668B7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -836,7 +1031,7 @@
 </file>
 
 <file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9DF4B14-955E-45D3-8B06-6FC9C1BAE562}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79342C9F-0DB6-470C-93E1-A757164BF0E8}">
   <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -847,7 +1042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A40FB9DF-E2BA-4A3F-8A23-6A5A02C6EBC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF384E9-814A-4027-A3C3-32C0D4874E5B}">
   <dimension ref="D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -859,7 +1054,7 @@
 </file>
 
 <file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC5B684-A91B-4A55-8DC9-BF8199E8239B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09D3C62-0ACE-4380-BF36-F75E63C53A7F}">
   <dimension ref="B3:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -879,7 +1074,7 @@
 </file>
 
 <file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E42AB45-9CA2-4092-B3D0-3EEE623E06DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E92D18-7E94-4FD6-8924-CB4C59C4445F}">
   <dimension ref="A3:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -891,7 +1086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ADF6D7-7E03-4AD4-AE24-93836524F86F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6B00AB-4402-4DA7-BB81-4622E430BA36}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -900,7 +1095,7 @@
 </file>
 
 <file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9BAD04-5299-4E95-88F0-5503675E5729}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0A18399-CC4F-4347-9983-35BF7668EB92}">
   <dimension ref="C1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -913,7 +1108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DDC4990-E86B-4FB8-8223-4A2AA6F2E146}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398F1C8B-6390-40D8-A988-1DFE325A2333}">
   <dimension ref="D3:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -928,7 +1123,7 @@
 </file>
 
 <file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B07F39-73D5-400C-BACF-EEFE94ECD91A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A594EBA3-A896-4136-B8BD-11FDEA8CC0AB}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -940,7 +1135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet109.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EF235D-112E-4F01-BB1C-AE6DE29A9A45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B71E1E-6D0D-4373-A1AA-CB5A35EA7F26}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -952,7 +1147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA1CBAD-F6E4-40FC-98A7-4CD5C3039956}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{404B5019-0172-41EE-AD6D-8FAE803C9C4D}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -965,7 +1160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet110.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A982DF7E-0447-4D47-A907-71402349CADA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13C8F77-5BCE-493C-8690-65352F673DF9}">
   <dimension ref="B2:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -979,7 +1174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet111.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04549C31-D72E-4DE7-A7A0-C65B7AD1E836}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E87625F-521E-4E3A-9668-4A867CABBFD1}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -990,7 +1185,7 @@
 </file>
 
 <file path=xl/worksheets/sheet112.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6997A7-905A-4DD3-B336-0CCB3FD8BC00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F299BD-2630-4B79-8241-D3AEC6A3E9C4}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1003,7 +1198,7 @@
 </file>
 
 <file path=xl/worksheets/sheet113.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFE421D-293C-40C3-9F71-2BCF601E3B31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329CA9CF-4040-4FD0-9EE6-B23F0D32B7BD}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1014,7 +1209,7 @@
 </file>
 
 <file path=xl/worksheets/sheet114.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9557C91C-685F-44BC-A4C8-5BAFCA0EC2F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57C58D0-1EAA-43A8-BA32-047C31C8E806}">
   <dimension ref="A3:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1030,7 +1225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet115.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E897BF8-482F-4C08-BC4D-D41652DF42F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE59A6E-BAF9-43C8-8479-9BEB56A3C586}">
   <dimension ref="A3:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1048,7 +1243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet116.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87496E03-C1DE-4D04-8B41-D054D9768CB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7CA571-5C60-4A9C-8642-CCBD96CA6B1E}">
   <dimension ref="A3:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1060,7 +1255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet117.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37364691-F6A8-427E-BB2A-C6160B28ADA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856D7DFA-8A9D-468B-BC15-0E74676807F0}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1071,7 +1266,7 @@
 </file>
 
 <file path=xl/worksheets/sheet118.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A191DC3-5986-4303-A527-87B4D21A469F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807C54F4-7922-4420-AC52-5DC1369549AE}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1082,7 +1277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet119.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC91285-D1C6-4D5C-9F6A-942E48F63BCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC730AE-1F52-4EB0-89C2-121647B869D1}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1095,7 +1290,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA43C383-3B7F-4730-AF71-C9CFCF310D73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7E2B51-B755-4A31-B287-60EBF0902E7E}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1108,7 +1303,7 @@
 </file>
 
 <file path=xl/worksheets/sheet120.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47EBA33-9123-49AA-9BB5-0143C96375E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE3A76F-3CCF-4C56-ACD2-9BFA00D83B74}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1119,7 +1314,7 @@
 </file>
 
 <file path=xl/worksheets/sheet121.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C214C91-E620-4648-9CE3-1B3F8257524A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78EC998E-865E-43E1-BC3C-2A8F11AA422B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1130,7 +1325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet122.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41175FCF-1FD6-443E-B886-C8004EC3FF19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEC859D-01FC-4445-8D3B-1DEB5C8A2FB3}">
   <dimension ref="A1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1141,7 +1336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet123.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D859C211-83E9-4A6B-A616-1D7210088AE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0420B7C2-092C-4253-A5A9-2B7AC778EF98}">
   <dimension ref="A2:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1161,7 +1356,7 @@
 </file>
 
 <file path=xl/worksheets/sheet124.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA507478-C603-42FE-8F70-69F80B6AE034}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C9101F-826F-4C54-AB70-72CDE4A63FB0}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1177,7 +1372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet125.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7512165-6B26-421C-A8C3-487CF5C20E4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975BBA00-F233-4F60-B66A-F483DDF0DB08}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1188,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F98EC2-61DC-43EC-800F-06BA59A162A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5BB4CB-41DD-41AC-A9BA-A848D44553C7}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1200,7 +1395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577503B4-1B53-425F-A7F7-DD34BEBE3EC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21AF2FA8-1ADC-44CF-8F73-3C0F14BEF539}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1212,7 +1407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7019C2DF-2C23-43D0-B8C1-AF388CC9E876}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CA49A19-FACB-478F-91A3-B9174E974386}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1224,7 +1419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E9B13D-3357-42B1-8DCB-369AF77F8240}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EA9B00-075D-4556-AF62-9F771F45F403}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1236,7 +1431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E858615-E253-46AB-93FA-BF89ECE5A12A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F514F8C-1320-40F9-97E3-7B62A820F9FC}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1249,7 +1444,7 @@
 </file>
 
 <file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B323CF29-9A5B-46B1-8AFA-2C8A8F428ACC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB6B7C7-8051-431F-84D1-7F0510630EF8}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1267,7 +1462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet131.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3EA86F-3830-43F0-ABDD-BD7CAFD89373}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A7C14B-AAF7-4D7D-B3ED-41910AE66BB8}">
   <dimension ref="C1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1280,7 +1475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet132.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA2E366-2E21-424D-8FD5-DFCEAECCA630}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2545C3A4-A520-4317-8B02-F7C26C9C8243}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1292,7 +1487,7 @@
 </file>
 
 <file path=xl/worksheets/sheet133.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9A10FA-D618-470B-8708-AC513CDE790E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8895400-B16F-417D-B315-E4EED92F03DA}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1304,7 +1499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet134.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DD6629-5AA3-4712-87DF-19FD8863D5CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC6C6E3-C8A6-4AFC-97D8-E71A4D624821}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1316,7 +1511,7 @@
 </file>
 
 <file path=xl/worksheets/sheet135.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5618DF46-AE8D-4DAA-BCCC-2FBBE5117BD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1DCF02-2573-4270-AA8D-1F3B3ED11DC8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1328,7 +1523,7 @@
 </file>
 
 <file path=xl/worksheets/sheet136.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D4460E8-3870-4C40-9B91-2872CF91FB3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF7978C-7948-4903-90F5-AE4F3492FAE9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1340,7 +1535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet137.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD527233-B0BF-4C34-8362-5B8591EBFD7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132DB19F-B4FB-4551-8D63-348DA2042890}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1352,7 +1547,7 @@
 </file>
 
 <file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E35418-2FE9-4593-9A1D-63E71A1659CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46D4EB9-4568-4D19-9D88-076F0EB9BF8D}">
   <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1363,7 +1558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet139.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB07BC8-A8FC-45D7-A4BC-A984525C23AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95175C62-7F50-4BDC-B556-11DD559A9966}">
   <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1374,7 +1569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15CEDBE-8D59-4945-BD2F-F8969C61B0D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E600F9F5-111D-46AA-A9C8-9678EF66A941}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1387,7 +1582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet140.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED3BE52-2962-497C-8B69-96DC593A79D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E24F08-270F-4929-9A4C-89FEEA1636D4}">
   <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1398,7 +1593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet141.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6147CB11-58D2-42BA-B0BB-21352AD03340}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94CD62E0-634F-4724-B379-E1FAE5C1FD62}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1411,7 +1606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet142.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4ED1C72-2B4C-4D8F-A286-1D3793B82AED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6809366C-F49D-4452-ADD2-B96BE10FC00F}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1426,7 +1621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet143.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41C5A8F0-576D-4B69-8434-D6B99A73F4EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D03087-C084-4F84-889C-BD48E2BBD2B4}">
   <dimension ref="B7"/>
   <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1444,7 +1639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet144.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3BE262-83FF-4813-AB64-A0B68579ED97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A25F98A0-60A3-43E9-A9DE-38B7E464C3A4}">
   <dimension ref="B7"/>
   <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1460,7 +1655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet145.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78642318-FFAC-467A-899F-058684777443}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4379E3A3-C464-40D9-9721-A465F82C4B0A}">
   <dimension ref="B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1472,7 +1667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet146.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C49181A-04C8-4095-A074-24EECD64CB5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D3D1479-01B2-41A4-933A-C6276B3777A0}">
   <dimension ref="C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1486,7 +1681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet147.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E1D6AA-0D02-4A05-957E-1593B3660BDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE7CE7B-7A2A-4C6B-BD21-74B4079D69D5}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1502,7 +1697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet148.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78DE2E6-D6AE-46A5-997F-901324485693}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB6EA4D-FB68-4A2E-8088-79204545831F}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1513,7 +1708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet149.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB4865C9-5866-4035-B2BF-E93CDC02EBD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F3B33-30D5-44E8-9C4A-C91038F9A80E}">
   <dimension ref="C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1529,7 +1724,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE870EDC-1FE6-4C57-9671-3D097604F0F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA08F499-E6D6-415E-B379-DCC3B45F814B}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1541,8 +1736,140 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet150.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B3CCF83-1CC4-4E29-A3F4-794727E716CE}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet151.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A193CF6C-14B3-4D07-9FFA-B48E9E88F420}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet152.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86D6D02-5046-405B-8507-40768CF2CF6A}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="36"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet153.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B413AB85-5587-4A91-B005-795DF5B8AA9F}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet154.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6A3E4F-3910-47AB-981A-6DB29281E078}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet155.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{486B9568-4053-471D-BDFF-D12480994D6B}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="40"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet156.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96C2291C-88D7-4333-9C6D-403D64D969B3}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="41"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet157.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5C916F3-4E05-452C-A0B1-2E14C19B6F80}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="42"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet158.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F33440ED-3B55-460E-9B10-B2BC9AFF3A3A}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="38"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet159.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700DB21A-9661-4EC1-857E-7C743FA80784}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="43"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E71F86-F92F-45EE-8E85-35F661F9255F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E0C8A2-B349-41B4-8210-16CA1FD907A0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1550,8 +1877,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet160.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3866A1CA-D771-4EA8-8458-0375B6419FAF}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet161.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA68DBA6-DE5D-4A40-BEAD-6DB1DEE374C5}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="45"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet162.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC201A8B-BF04-4173-89AE-42C9764C1C2B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet163.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A2615F-52C7-4E25-9370-A8D4D87A7CAD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet164.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02134178-D243-49D0-8D2E-AE9B23BF7396}">
+  <dimension ref="B1048576"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1048576" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1048576" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet165.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619A05E0-FFF6-4A9E-BB73-F65D4444807C}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="47"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet166.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5496C60-4C46-4DE6-B741-5AEC0E05CEEC}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="45"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet167.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{528D3817-954B-4811-A433-F64397904C29}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet168.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C92289-FF1F-42FF-A650-D9717C14598D}">
+  <dimension ref="B1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:2" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="48"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet169.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F16BD8A-C458-4B3B-A381-CCF12E8E6DB1}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{682446D6-8A26-475F-8C80-1D66CE543FB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52059C6A-8542-4F17-85A9-4AE63284AA93}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1563,8 +2031,142 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet170.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5C9535-AF7C-495C-A115-7C9B7AF77A31}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="50"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet171.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8539A95A-3972-4AF3-B541-929ADECE82A9}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" s="32" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="51"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet172.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{182E552E-DBF6-4D45-9E83-3693D62F6B01}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet173.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E110E8-B3F8-482D-A49D-9088AD57EAB3}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet174.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BF03387-A579-4727-A4C7-C0967DEA9216}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet175.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50EB390-8019-487D-AEC5-FF00A32D5544}">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" s="37" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet176.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9500366-0B10-42BC-A765-EF4BF08BD737}">
+  <dimension ref="XFD2:XFD3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="16384:16384" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="XFD2" s="37"/>
+    </row>
+    <row r="3" spans="16384:16384" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet177.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31AC09CC-8AE9-4DCE-93C6-FBED4E8D9705}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet178.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229F4E2E-70A6-4908-AAF8-EB3B782360A3}">
+  <dimension ref="C1"/>
+  <sheetFormatPr defaultRowHeight="16.5" thickTop="1" thickBottom="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" style="48"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet179.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90EE291-851C-450D-8D43-FE0283B33F9D}">
+  <dimension ref="C1"/>
+  <sheetFormatPr defaultRowHeight="15.75" thickBottom="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" style="49"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8443D34-C7B4-437B-A8B4-19D953BCFAFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E90B41F-CA4D-480B-A966-2F65AAB45454}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1576,8 +2178,141 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet180.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780EBF8D-7CF7-4CE3-AE46-5CA491C58E15}">
+  <dimension ref="C5:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" thickTop="1" thickBottom="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet181.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6C786E-C7BD-4B2B-A919-F32E560E7819}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" thickTop="1" thickBottom="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="48"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet182.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{528208D5-B235-42B0-80D3-9B4337C7D6EC}">
+  <dimension ref="B2:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+      <c r="C2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet183.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BCE1FDF-52BF-4860-A763-3AADF6156525}">
+  <dimension ref="B2:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+      <c r="C2" s="35"/>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet184.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97AADC0-E96B-474D-A8DA-AF309716CC73}">
+  <dimension ref="B2:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+      <c r="C2" s="35"/>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet185.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D56FB6E-5E2F-4D95-8185-7A2D542BD672}">
+  <dimension ref="B2:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="21"/>
+      <c r="C2" s="37"/>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet186.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B54EE447-78DE-4A46-8D76-577870566686}">
+  <dimension ref="B2:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet187.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FDB33F7-6B20-4996-A45E-D6B55F0CA8B9}">
+  <dimension ref="C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="3:3" s="37" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet188.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E86560-56F0-41E2-A7AD-24BD021F416B}">
+  <dimension ref="B2:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+    </row>
+    <row r="3" spans="2:2" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFB0464-0F80-4068-9C8F-3C0216CA059E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756D7260-CFB1-4D3C-9CF0-472ACC8B7803}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1592,7 +2327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63646BB-8B61-48EB-BD25-73950AB4D9F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A49B56BE-05E7-483E-A410-94F6FA63BC50}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1605,7 +2340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B61C58-5F8F-4B32-8037-46CCCB4BD9D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E24501-E3B2-4FA9-8BBC-86E06E6A3F76}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1620,7 +2355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E553063-E94B-40AB-B30F-9489678A8AEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47120F3-4641-4BD2-9F8B-059A274A8EB4}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1633,7 +2368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F517E25E-06F1-4789-9940-E579EF36F4D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9110B6FF-D087-41B4-8583-FE4528221097}">
   <dimension ref="B2:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1647,7 +2382,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD8909DB-78EB-48FC-9515-EDD1C49A7755}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD89DF1-2D4B-413E-9EF8-0A25210288DA}">
   <dimension ref="B2:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1663,7 +2398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17F3C3B-0AB4-4013-AD4A-C7455AF8A6EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EAA8879-2C03-4557-B4F2-BFB7DB18E3C9}">
   <dimension ref="A3:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1682,7 +2417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2F0D92-D627-4848-AE7C-4925E272D6F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5F4B5D-4DC2-4798-93AF-FFD8756A17E7}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1693,7 +2428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721A21F5-D936-4CB8-8CDC-AD2149274DE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A251B8D3-6346-41BA-B32B-078D3B66B9A5}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1705,7 +2440,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5E812-F947-4A23-AB09-0E36872AE00C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC041A9A-0CED-434D-9482-CB8A749725F3}">
   <dimension ref="C1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1728,7 +2463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38435EB-7E01-4118-AD3B-8D9C16137F59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654FA337-B47A-4F5D-B60C-6884063424C6}">
   <dimension ref="E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1744,7 +2479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A08606E-BA13-47C6-8348-2F43617FBB27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E42D5D-F376-48AB-B5E9-1788ACF80FC2}">
   <dimension ref="E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1760,7 +2495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D5D747-E0F2-4738-8D7B-7A501D6CFFAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9345C0BB-B56C-44EA-9337-DAAFBC1B8CB4}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1773,7 +2508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F627EE5D-1160-4AE4-80A1-86E01B4D1BC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E132F3-36D8-4A77-BA27-2E7FE02CEC65}">
   <dimension ref="E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1787,7 +2522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA0C26D-0519-4E84-8478-87B0EEA449D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD6D075-FE35-4F58-B8C9-39323DAA275C}">
   <dimension ref="E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1801,7 +2536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203C7972-A992-4980-8D46-71F0035089FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B04733-84CE-4517-8848-5BCB4D539D4F}">
   <dimension ref="E5:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1825,7 +2560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF3D825-DE28-4348-8B81-D894118751CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90B10A64-6CFF-4FD0-A659-769294A55D92}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1836,7 +2571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C595C0A8-8819-4092-9CF8-68FB6CCCAB11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{145035BE-8A9D-4D93-8445-B9D01E4C5423}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1847,7 +2582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF94585-19C4-45C3-A4B1-67FAEB5FA884}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A1AA13-8C92-4A37-A779-46AD85BC7E8A}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1859,7 +2594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72511200-E4F8-45EE-8603-BFE085DA3A90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{754A4D52-D917-4D1E-84B2-23CBCDC67847}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1871,7 +2606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F53F219-E33A-4697-B3AF-776D1FA6DC85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001A6329-5C46-438B-80A1-4E1262061F82}">
   <dimension ref="A3:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1884,7 +2619,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5043C5BC-E2E1-4DD1-BF3F-994493D6EF0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B6EA03C-9568-48D3-9D13-CA60759E024E}">
   <dimension ref="A7:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1896,7 +2631,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45254762-2037-450F-B223-0543CF79D3A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341D4104-70F7-41AC-87E9-BDD3F196C116}">
   <dimension ref="A9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1907,7 +2642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5961AB99-D1A4-48D2-98B0-A8B716DCA662}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{996C3474-7A56-410C-B530-8E4D147A87D5}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1920,7 +2655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{136568C4-5FAB-404A-AA14-AF9C8129F51F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB35A3FF-0ED4-437A-9923-5BE7515CC149}">
   <dimension ref="B1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1932,7 +2667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A72DCEB-9317-4A5B-A467-BB00EF4FF1EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B3B666-38AB-4DD2-BE64-440230FF28C0}">
   <dimension ref="B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1947,7 +2682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E33E6F-F158-4B49-A5B1-758A446D117E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4ED0AD-8DB9-4A82-AED4-30352CFC5D13}">
   <dimension ref="C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1965,7 +2700,7 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBEAA0C-746B-415F-BF2A-4FF1C599E066}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3071598D-1D64-4676-9123-73841ADFCDD6}">
   <dimension ref="XFD3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1980,7 +2715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094EECA3-C48E-4A4B-A4C9-341C0914510E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF44A162-9B3E-4F6C-8566-DAA0A9108E82}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1992,7 +2727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1977F19B-3A79-4027-B70E-B3057723F157}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC83ED7-2327-4B94-A09C-9FAE0E74F849}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2004,7 +2739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47257BBD-1845-421E-8D47-61F26E224D75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5812C3-3949-44A2-8F70-CCBC90C59382}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2016,7 +2751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E2F147-9273-4E14-80B4-9C399295D6D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F3C1EE-0F0B-49A4-93B9-04A5C9AD5F16}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2027,7 +2762,7 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9372A77C-4817-461E-A3FF-7861F685483E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5761182-B49E-4E7F-A7CA-0EF8F03F92B1}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2038,7 +2773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B8AFDF-816E-4413-BF1B-58CA22E6834C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01FCCD1B-544D-4159-BB2B-9AF2645B54DF}">
   <dimension ref="C3:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2054,7 +2789,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{248DD116-B8DD-4E83-AEB0-39C1F931E5A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{428B8087-E101-4B2D-98EC-4BA6AD5AA831}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2067,7 +2802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{597681E5-86BF-433F-A514-7EA893C1FC90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87BF6BBF-2474-49D0-A217-7C4D317F11CC}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2078,7 +2813,7 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2305D80-16B4-4298-8522-74C92587F173}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BA3E8A-672A-4D33-9625-D16C5D3878B0}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2089,7 +2824,7 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC1F89C-8A2A-42B1-B272-D49E46359A08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FC62FA-0B95-4A36-A8F6-FAB30EAE3C04}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2102,7 +2837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB19965-56CA-4B67-9366-29A2195F3260}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A933FC-23B6-458B-8BE6-D060777F4BCE}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2115,7 +2850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D5CE1A-ED8B-4105-BA81-926E0B372A6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2CAD93-EBA8-4100-9F08-8376C4ED5136}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2126,7 +2861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8897B106-71FD-4593-B437-B1CC0AE4D478}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE55FF9-8C5C-4CFC-A467-1DA993F3BAF7}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2137,7 +2872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{311407F2-F0D8-4C2A-A3F1-0B6DA5589496}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C400F4B9-5FDE-4A67-B035-FB87EDBC2D5F}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2150,7 +2885,7 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED0D858-FA48-4509-9CF1-79E4AC50BA1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69653943-B691-4EC8-A434-B418A35452D2}">
   <dimension ref="B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2163,7 +2898,7 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E82BBD-268C-4407-B80A-C010E7FC6E28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3833C32-2C8B-4681-B3E4-46FB69AA9B43}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2178,7 +2913,7 @@
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4663EC89-9202-4E07-A5DD-6CB9C4D5C134}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D24DEEE-9DBC-4145-A34C-5CBABEDA644D}">
   <dimension ref="C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2193,7 +2928,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197B6468-11D5-4ED5-ADD8-8EE7E5C6EC91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC582D7-79AF-4369-AB57-90890E515AEF}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2206,7 +2941,7 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0E75EA-5EB3-4B86-B715-9C34BDC517B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC66905-AE1C-46B7-951D-B9DE6CF55B57}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2217,7 +2952,7 @@
 </file>
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7800BB-FE74-48F1-BF65-D9B2DEFECECE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4D1DAB-ED4D-4708-9CA6-581FB904C36D}">
   <dimension ref="C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2233,7 +2968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5117C65-652E-47A5-B43E-4B2559610087}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9011D17E-8718-4B65-BD76-E79211B294EC}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2245,7 +2980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64280D42-12DA-4708-B55E-FE2C68E1FE8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A67134-01AD-4D68-8131-FAE67F43891E}">
   <dimension ref="E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2261,7 +2996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03251DB5-CC60-4C32-92EA-D6A202EE5DBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BDDDC23-C12A-4D25-AC64-1D622B35A215}">
   <dimension ref="E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2277,7 +3012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE78341-1DF4-4736-B6DA-E10E8B52FF68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE05344-52C8-4BB2-B1BC-9D712C5A26E2}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2293,7 +3028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E86EAB-488F-4910-BCCC-7E6BEB4D61B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4478D358-FBCC-41BF-A072-20C6A48E1374}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2309,7 +3044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAE2C9E-809E-457E-AFEA-7902E1017D3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A92C1D-4130-4D00-ABFE-233F38113A3B}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2322,7 +3057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620AC5E3-927B-474E-BA14-6A2E8A99CD5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D680B1B3-2CCC-49B5-A242-60DE859774DF}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2335,7 +3070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0377DC11-B035-4284-B3CE-9E70563D421A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A715F91F-F284-4536-A89E-3E1921EEBE53}">
   <dimension ref="B3:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2350,7 +3085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A89C543-0643-49C0-B586-7F8D23BFC3EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59FB4495-6F98-4F6A-9387-3F4CCD3B23C5}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2363,7 +3098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD64B02-C655-42FA-96CC-3FF8D94647E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{813EE044-0BAC-4072-9A2C-FFF7C60F0201}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2372,7 +3107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A19F7C5-FBDD-43FA-8189-C2654F69DCD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E001CF-5CDD-492F-9070-36CAA0CF936F}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2383,7 +3118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA01018-D48E-4733-8AE6-54ED2684F374}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD5EFC6D-72CD-4D1C-8C2B-6D1D293FC552}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2401,7 +3136,7 @@
 </file>
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924FD371-0031-48C0-B700-25CAAA408AF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21CE12D8-3411-43A4-BE64-F9302904EED2}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2415,7 +3150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB308BF-CC27-4A36-BE3B-CDE05B21158B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D1FFEB-8511-46D0-A906-BC645D5B8217}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2429,7 +3164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F987DC71-CA77-4121-9555-BA2D3F4FE0BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D015DF1-3B3E-4D2B-854A-B8E0E693CFAE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2441,7 +3176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32B274E-C527-4E05-B25C-4914021E2983}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E700638A-3029-4340-852B-558501ADFA22}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2454,7 +3189,7 @@
 </file>
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A3AB43-FECE-4AC9-A68E-79DB67B07822}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CA1338-506C-4EBA-AC1D-53999107C187}">
   <dimension ref="A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2468,7 +3203,7 @@
 </file>
 
 <file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27EE149C-63D1-4474-BB11-AD908932FFE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A37C2AD-703F-4ECD-90AF-8202B196C61C}">
   <dimension ref="D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2482,7 +3217,7 @@
 </file>
 
 <file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C880BA2F-CD8B-4667-8C71-9C2B5C3C4A40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA347AF0-E9A8-4337-A56D-044E12086DA0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2491,7 +3226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF16CAA1-F70A-438F-9616-4AE210CB80A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0EF8CE-9FEF-4701-BE22-7967CE7A81C5}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2504,7 +3239,7 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674A7559-2B52-4B9C-A29C-670DFCF37F4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE78B068-5DF5-4C2A-BC94-4169A3CDD851}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2522,7 +3257,7 @@
 </file>
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F0E5D10-96F8-4161-A1C4-1B7FFE67B57D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AA88B6-22DB-4A2A-8C20-33956FBD60E1}">
   <dimension ref="XFD1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2540,7 +3275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FA95AB-6963-4B73-A68F-4A6262C79F47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9BAD54-108B-412C-A8C3-C1FE79B73143}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2554,7 +3289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4D839B-E358-4A8B-A3EE-21EDF410C1D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998225D8-D14C-4D4F-BA16-2A968833010D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2568,7 +3303,7 @@
 </file>
 
 <file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C92BA1B-7926-4784-93A3-2CAB458EAA84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1283D7A7-BC4A-402C-8BD3-3E03CDA59A6B}">
   <dimension ref="A1:XFC1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2580,7 +3315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEA5BC7-2769-43BA-B363-54F471BF7031}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{346DEA11-4D23-4FCE-8A28-0B2A5E7B73FD}">
   <dimension ref="A4:XFC4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18978,7 +19713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74683EAB-A4A6-4D17-AC63-24E0D04A7F6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B29534-E96F-46C4-9FCD-B764F48016E7}">
   <dimension ref="A3:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18990,7 +19725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A6EB16-A6D1-46E2-98E7-511997B3497A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50DFE10-9745-4998-B7BC-CD2868BDDA08}">
   <dimension ref="A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19001,7 +19736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A456C46B-BB25-4AA1-871A-D55EA483D256}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5820D56-4E88-4AE5-9F69-A06D4649EA79}">
   <dimension ref="A2:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19014,7 +19749,7 @@
 </file>
 
 <file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D9642C-CA43-4DCE-940C-F7B5385F20E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E7F556-6D4D-4BC4-A3FC-AB5AEC7094B8}">
   <dimension ref="A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19025,7 +19760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{296D1E27-76E5-4ECC-8E9C-DF9455A4DA7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4DB8409-6040-4D15-98BA-3E57FCC090F3}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19038,7 +19773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DB7825-947E-4F9A-AD79-0404CC928D06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7ACEAB-6AF5-452D-BB88-912CE121B46E}">
   <dimension ref="A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19049,7 +19784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038EE046-24CE-4AA4-A495-188D74238221}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B210826-0835-4633-A786-346EEC020393}">
   <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19060,7 +19795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF9BCF9-5056-4599-80D4-534F72959762}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93367A94-384D-447B-9AD1-F15B72BFBF66}">
   <dimension ref="B3:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19079,7 +19814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7839C5D-FA28-4EA3-B6E6-DAEB66BE7F01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C555EFAC-B864-4C16-B872-E091BEBF97D4}">
   <dimension ref="B3:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19098,7 +19833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC431342-E05B-4BAC-82A0-FA161E473E2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F4A568-A657-4C8F-8EBB-A2C0972D048E}">
   <dimension ref="B3:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19117,7 +19852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE4D091-000C-4D2B-B34D-26D6334466CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8834C149-B24B-4030-BC00-AEF002AA7CCC}">
   <dimension ref="D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19129,7 +19864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D30C3A3-E683-4D18-B0ED-E8293778B066}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100D5CF5-5DF6-444D-9564-3CE7535D9E0D}">
   <dimension ref="C2:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19143,7 +19878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E8E389-72F1-42EC-BC87-4D2769938C8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE366C1-2D66-4BF5-9F1E-DE3640F5CE8E}">
   <dimension ref="C1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19155,7 +19890,7 @@
 </file>
 
 <file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D841F51E-45AA-4470-8D91-6BBDD3AE1B8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D766F310-B1A9-4DE9-B681-C6A2871B598A}">
   <dimension ref="A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19166,7 +19901,7 @@
 </file>
 
 <file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E79E011-183E-416B-A1F4-FE857D68E781}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F0DE8E-2C0D-4A2B-9752-5043C54C1E7A}">
   <dimension ref="A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/tests/fixtures/row_formats/row_formats.xlsx
+++ b/tests/fixtures/row_formats/row_formats.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmp8pn_8tbf\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{610F70AC-3DBE-4515-B9B4-5C6982D5FA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="7920" windowHeight="13995" firstSheet="187" activeTab="187" xr2:uid="{4318A891-E76C-4392-8907-219407430D5D}"/>
